--- a/Src/Data/Tables/ItemDefine.xlsx
+++ b/Src/Data/Tables/ItemDefine.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" updateLinks="always"/>
   <bookViews>
-    <workbookView windowWidth="21096" windowHeight="9815" tabRatio="599"/>
+    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="599"/>
   </bookViews>
   <sheets>
     <sheet name="Elements" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="198">
   <si>
     <t>名字</t>
   </si>
@@ -65,6 +65,9 @@
     <t>销售价格</t>
   </si>
   <si>
+    <t>品质</t>
+  </si>
+  <si>
     <t>功能</t>
   </si>
   <si>
@@ -128,13 +131,16 @@
     <t>SellPrise</t>
   </si>
   <si>
+    <t>QualityColor</t>
+  </si>
+  <si>
     <t>Function</t>
   </si>
   <si>
     <t>Param</t>
   </si>
   <si>
-    <t>列1</t>
+    <t>列2</t>
   </si>
   <si>
     <t>小型治疗药水</t>
@@ -152,6 +158,9 @@
     <t>UI/Items/hongp</t>
   </si>
   <si>
+    <t>Green</t>
+  </si>
+  <si>
     <t>RecoverHP</t>
   </si>
   <si>
@@ -179,6 +188,9 @@
     <t>UI/Items/mbao</t>
   </si>
   <si>
+    <t>Blue</t>
+  </si>
+  <si>
     <t>AddBuff</t>
   </si>
   <si>
@@ -191,6 +203,9 @@
     <t>UI/Items/haixiant</t>
   </si>
   <si>
+    <t>Purple</t>
+  </si>
+  <si>
     <t>小型经验书</t>
   </si>
   <si>
@@ -585,6 +600,9 @@
   </si>
   <si>
     <t>UI/Items/ride8001</t>
+  </si>
+  <si>
+    <t>Orange</t>
   </si>
   <si>
     <t>夜行虎</t>
@@ -1422,7 +1440,7 @@
     <cellStyle name="好 2" xfId="59"/>
     <cellStyle name="适中 2" xfId="60"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
     <dxf>
       <font>
         <name val="微软雅黑"/>
@@ -1674,6 +1692,21 @@
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1685,9 +1718,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A3:Q58" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:Q58" etc:filterBottomFollowUsedRange="0"/>
-  <tableColumns count="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A3:R58" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:R58" etc:filterBottomFollowUsedRange="0"/>
+  <tableColumns count="18">
     <tableColumn id="1" name="Key" dataDxfId="0"/>
     <tableColumn id="3" name="ID" dataDxfId="1"/>
     <tableColumn id="5" name="Name" dataDxfId="2"/>
@@ -1702,9 +1735,10 @@
     <tableColumn id="11" name="StackLimit" dataDxfId="11"/>
     <tableColumn id="12" name="Icon" dataDxfId="12"/>
     <tableColumn id="13" name="SellPrise" dataDxfId="13"/>
-    <tableColumn id="14" name="Function" dataDxfId="14"/>
-    <tableColumn id="15" name="Param" dataDxfId="15"/>
-    <tableColumn id="16" name="列1" dataDxfId="16"/>
+    <tableColumn id="14" name="QualityColor" dataDxfId="14"/>
+    <tableColumn id="15" name="Function" dataDxfId="15"/>
+    <tableColumn id="16" name="Param" dataDxfId="16"/>
+    <tableColumn id="17" name="列2" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1997,7 +2031,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr defaultColWidth="16.287037037037" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="2" width="11" style="2" customWidth="1"/>
@@ -2013,7 +2047,7 @@
     <col min="14" max="16384" width="16.287037037037" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:16">
+    <row r="1" customHeight="1" spans="1:18">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4" t="s">
@@ -2058,111 +2092,120 @@
       <c r="P1" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="2:17">
+      <c r="Q1" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:18">
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="H2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="L2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="M2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="4" t="s">
+      <c r="O2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:17">
+      <c r="R2" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:18">
       <c r="A3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:16">
+        <v>36</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2170,16 +2213,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G4" s="1">
         <v>1</v>
@@ -2197,19 +2240,22 @@
         <v>99</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N4" s="1">
         <v>100</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" s="1">
+        <v>43</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:16">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -2217,16 +2263,16 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -2244,19 +2290,22 @@
         <v>99</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="N5" s="1">
         <v>100</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P5" s="1">
+        <v>43</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q5" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:16">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2264,16 +2313,16 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -2291,19 +2340,22 @@
         <v>99</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N6" s="1">
         <v>100</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="P6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:16">
+        <v>53</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2311,16 +2363,16 @@
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -2338,19 +2390,22 @@
         <v>99</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="N7" s="1">
         <v>100</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="P7" s="1">
+        <v>58</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q7" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2358,16 +2413,16 @@
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -2382,7 +2437,7 @@
         <v>99</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="N8" s="1">
         <v>1</v>
@@ -2390,8 +2445,11 @@
       <c r="O8" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="P8" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -2399,16 +2457,16 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -2420,13 +2478,16 @@
         <v>500</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N9" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:16">
+      <c r="O9" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:18">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -2434,16 +2495,16 @@
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -2458,19 +2519,22 @@
         <v>10</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="N10" s="4">
         <v>1</v>
       </c>
-      <c r="O10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="P10" s="4">
+      <c r="O10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q10" s="4">
         <v>1000</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:16">
+    <row r="11" customHeight="1" spans="1:18">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -2478,16 +2542,16 @@
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D11" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -2502,19 +2566,22 @@
         <v>10</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N11" s="4">
         <v>1</v>
       </c>
-      <c r="O11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="P11" s="4">
+      <c r="O11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q11" s="4">
         <v>10000</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:15">
+    <row r="12" customHeight="1" spans="1:18">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -2522,16 +2589,16 @@
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G12" s="2">
         <v>10</v>
@@ -2546,16 +2613,19 @@
         <v>1</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="N12" s="4">
         <v>1</v>
       </c>
-      <c r="O12" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:16">
+      <c r="O12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:18">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2563,16 +2633,16 @@
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -2587,19 +2657,22 @@
         <v>1</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="N13" s="4">
         <v>1</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="P13" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:14">
+        <v>53</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:18">
       <c r="A14" s="2">
         <v>1001</v>
       </c>
@@ -2607,34 +2680,37 @@
         <v>1001</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L14" s="4">
         <v>1</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="N14" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:14">
+      <c r="O14" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:18">
       <c r="A15" s="2">
         <v>1002</v>
       </c>
@@ -2642,34 +2718,37 @@
         <v>1002</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D15" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="F15" s="9" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L15" s="4">
         <v>1</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="N15" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:14">
+      <c r="O15" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:18">
       <c r="A16" s="2">
         <v>1003</v>
       </c>
@@ -2677,34 +2756,37 @@
         <v>1003</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D16" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="F16" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L16" s="4">
         <v>1</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="N16" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:14">
+      <c r="O16" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:15">
       <c r="A17" s="2">
         <v>1004</v>
       </c>
@@ -2712,34 +2794,37 @@
         <v>1004</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D17" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="F17" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L17" s="4">
         <v>1</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="N17" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:14">
+      <c r="O17" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:15">
       <c r="A18" s="2">
         <v>1005</v>
       </c>
@@ -2747,34 +2832,37 @@
         <v>1005</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D18" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="F18" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L18" s="4">
         <v>1</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="N18" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:14">
+      <c r="O18" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:15">
       <c r="A19" s="2">
         <v>1006</v>
       </c>
@@ -2782,34 +2870,37 @@
         <v>1006</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="F19" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L19" s="4">
         <v>1</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="N19" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:14">
+      <c r="O19" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:15">
       <c r="A20" s="2">
         <v>1007</v>
       </c>
@@ -2817,34 +2908,37 @@
         <v>1007</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D20" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="F20" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L20" s="4">
         <v>1</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="N20" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:14">
+      <c r="O20" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:15">
       <c r="A21" s="2">
         <v>2001</v>
       </c>
@@ -2852,34 +2946,37 @@
         <v>2001</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G21" s="2">
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L21" s="4">
         <v>1</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N21" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:14">
+      <c r="O21" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:15">
       <c r="A22" s="2">
         <v>2002</v>
       </c>
@@ -2887,34 +2984,37 @@
         <v>2002</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L22" s="4">
         <v>1</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="N22" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:14">
+      <c r="O22" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:15">
       <c r="A23" s="2">
         <v>2003</v>
       </c>
@@ -2922,34 +3022,37 @@
         <v>2003</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="G23" s="2">
-        <v>1</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>103</v>
-      </c>
       <c r="L23" s="4">
         <v>1</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="N23" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:14">
+      <c r="O23" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:15">
       <c r="A24" s="2">
         <v>2004</v>
       </c>
@@ -2957,34 +3060,37 @@
         <v>2004</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L24" s="4">
         <v>1</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="N24" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:14">
+      <c r="O24" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:15">
       <c r="A25" s="2">
         <v>2005</v>
       </c>
@@ -2992,34 +3098,37 @@
         <v>2005</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L25" s="4">
         <v>1</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N25" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:14">
+      <c r="O25" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:15">
       <c r="A26" s="2">
         <v>2006</v>
       </c>
@@ -3027,34 +3136,37 @@
         <v>2006</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L26" s="4">
         <v>1</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="N26" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:14">
+      <c r="O26" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:15">
       <c r="A27" s="2">
         <v>2007</v>
       </c>
@@ -3062,34 +3174,37 @@
         <v>2007</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L27" s="4">
         <v>1</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="N27" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:14">
+      <c r="O27" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:15">
       <c r="A28" s="2">
         <v>3001</v>
       </c>
@@ -3097,34 +3212,37 @@
         <v>3001</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L28" s="4">
         <v>1</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="N28" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:14">
+      <c r="O28" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:15">
       <c r="A29" s="2">
         <v>3002</v>
       </c>
@@ -3132,34 +3250,37 @@
         <v>3002</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L29" s="4">
         <v>1</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="N29" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:14">
+      <c r="O29" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:15">
       <c r="A30" s="2">
         <v>3003</v>
       </c>
@@ -3167,34 +3288,37 @@
         <v>3003</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D30" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="G30" s="2">
-        <v>1</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>121</v>
-      </c>
       <c r="L30" s="4">
         <v>1</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="N30" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:14">
+      <c r="O30" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:15">
       <c r="A31" s="2">
         <v>3004</v>
       </c>
@@ -3202,34 +3326,37 @@
         <v>3004</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L31" s="4">
         <v>1</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="N31" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:14">
+      <c r="O31" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:15">
       <c r="A32" s="2">
         <v>3005</v>
       </c>
@@ -3237,34 +3364,37 @@
         <v>3005</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L32" s="4">
         <v>1</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="N32" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" customHeight="1" spans="1:14">
+      <c r="O32" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:15">
       <c r="A33" s="2">
         <v>3006</v>
       </c>
@@ -3272,34 +3402,37 @@
         <v>3006</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L33" s="4">
         <v>1</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="N33" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" customHeight="1" spans="1:14">
+      <c r="O33" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:15">
       <c r="A34" s="2">
         <v>3007</v>
       </c>
@@ -3307,34 +3440,37 @@
         <v>3007</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L34" s="4">
         <v>1</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="N34" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:14">
+      <c r="O34" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:15">
       <c r="A35" s="2">
         <v>1011</v>
       </c>
@@ -3342,34 +3478,37 @@
         <v>1011</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G35" s="2">
         <v>10</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L35" s="4">
         <v>1</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="N35" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" customHeight="1" spans="1:14">
+      <c r="O35" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:15">
       <c r="A36" s="2">
         <v>1012</v>
       </c>
@@ -3377,34 +3516,37 @@
         <v>1012</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G36" s="2">
         <v>10</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L36" s="4">
         <v>1</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="N36" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" customHeight="1" spans="1:14">
+      <c r="O36" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:15">
       <c r="A37" s="2">
         <v>1013</v>
       </c>
@@ -3412,34 +3554,37 @@
         <v>1013</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G37" s="2">
         <v>10</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L37" s="4">
         <v>1</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="N37" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:14">
+      <c r="O37" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:15">
       <c r="A38" s="2">
         <v>1014</v>
       </c>
@@ -3447,34 +3592,37 @@
         <v>1014</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G38" s="2">
         <v>10</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L38" s="4">
         <v>1</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="N38" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" customHeight="1" spans="1:14">
+      <c r="O38" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:15">
       <c r="A39" s="2">
         <v>1015</v>
       </c>
@@ -3482,34 +3630,37 @@
         <v>1015</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G39" s="2">
         <v>10</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L39" s="4">
         <v>1</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N39" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="40" customHeight="1" spans="1:14">
+      <c r="O39" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:15">
       <c r="A40" s="2">
         <v>1016</v>
       </c>
@@ -3517,34 +3668,37 @@
         <v>1016</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G40" s="2">
         <v>10</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L40" s="4">
         <v>1</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="N40" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="41" customHeight="1" spans="1:14">
+      <c r="O40" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:15">
       <c r="A41" s="2">
         <v>1017</v>
       </c>
@@ -3552,34 +3706,37 @@
         <v>1017</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G41" s="2">
         <v>10</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L41" s="4">
         <v>1</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="N41" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" customHeight="1" spans="1:14">
+      <c r="O41" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:15">
       <c r="A42" s="2">
         <v>2011</v>
       </c>
@@ -3587,34 +3744,37 @@
         <v>2011</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G42" s="2">
         <v>10</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L42" s="4">
         <v>1</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="N42" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" customHeight="1" spans="1:14">
+      <c r="O42" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:15">
       <c r="A43" s="2">
         <v>2012</v>
       </c>
@@ -3622,34 +3782,37 @@
         <v>2012</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G43" s="2">
         <v>10</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L43" s="4">
         <v>1</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="N43" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" customHeight="1" spans="1:14">
+      <c r="O43" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:15">
       <c r="A44" s="2">
         <v>2013</v>
       </c>
@@ -3657,34 +3820,37 @@
         <v>2013</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G44" s="2">
         <v>10</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L44" s="4">
         <v>1</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="N44" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" customHeight="1" spans="1:14">
+      <c r="O44" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:15">
       <c r="A45" s="2">
         <v>2014</v>
       </c>
@@ -3692,34 +3858,37 @@
         <v>2014</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G45" s="2">
         <v>10</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L45" s="4">
         <v>1</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="N45" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" customHeight="1" spans="1:14">
+      <c r="O45" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:15">
       <c r="A46" s="2">
         <v>2015</v>
       </c>
@@ -3727,34 +3896,37 @@
         <v>2015</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G46" s="2">
         <v>10</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L46" s="4">
         <v>1</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="N46" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" customHeight="1" spans="1:14">
+      <c r="O46" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:15">
       <c r="A47" s="2">
         <v>2016</v>
       </c>
@@ -3762,34 +3934,37 @@
         <v>2016</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G47" s="2">
         <v>10</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L47" s="4">
         <v>1</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="N47" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" customHeight="1" spans="1:14">
+      <c r="O47" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:15">
       <c r="A48" s="2">
         <v>2017</v>
       </c>
@@ -3797,34 +3972,37 @@
         <v>2017</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G48" s="2">
         <v>10</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L48" s="4">
         <v>1</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="N48" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" customHeight="1" spans="1:14">
+      <c r="O48" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:16">
       <c r="A49" s="2">
         <v>3011</v>
       </c>
@@ -3832,34 +4010,37 @@
         <v>3011</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G49" s="2">
         <v>10</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L49" s="4">
         <v>1</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="N49" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" customHeight="1" spans="1:14">
+      <c r="O49" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:16">
       <c r="A50" s="2">
         <v>3012</v>
       </c>
@@ -3867,34 +4048,37 @@
         <v>3012</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G50" s="2">
         <v>10</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L50" s="4">
         <v>1</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="N50" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="51" customHeight="1" spans="1:14">
+      <c r="O50" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="1:16">
       <c r="A51" s="2">
         <v>3013</v>
       </c>
@@ -3902,34 +4086,37 @@
         <v>3013</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G51" s="2">
         <v>10</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L51" s="4">
         <v>1</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="N51" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="52" customHeight="1" spans="1:14">
+      <c r="O51" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="1:16">
       <c r="A52" s="2">
         <v>3014</v>
       </c>
@@ -3937,34 +4124,37 @@
         <v>3014</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G52" s="2">
         <v>10</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L52" s="4">
         <v>1</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="N52" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" customHeight="1" spans="1:14">
+      <c r="O52" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="1:16">
       <c r="A53" s="2">
         <v>3015</v>
       </c>
@@ -3972,34 +4162,37 @@
         <v>3015</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G53" s="2">
         <v>10</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L53" s="4">
         <v>1</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="N53" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" customHeight="1" spans="1:14">
+      <c r="O53" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:16">
       <c r="A54" s="2">
         <v>3016</v>
       </c>
@@ -4007,34 +4200,37 @@
         <v>3016</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G54" s="2">
         <v>10</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L54" s="4">
         <v>1</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="N54" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" customHeight="1" spans="1:14">
+      <c r="O54" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:16">
       <c r="A55" s="2">
         <v>3017</v>
       </c>
@@ -4042,34 +4238,37 @@
         <v>3017</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G55" s="2">
         <v>10</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L55" s="4">
         <v>1</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="N55" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="56" spans="1:15">
+      <c r="O55" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
       <c r="A56" s="2">
         <v>8001</v>
       </c>
@@ -4077,16 +4276,16 @@
         <v>8001</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G56" s="11">
         <v>1</v>
@@ -4101,14 +4300,17 @@
         <v>1</v>
       </c>
       <c r="M56" s="12" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="N56" s="12">
         <v>500</v>
       </c>
-      <c r="O56" s="2"/>
-    </row>
-    <row r="57" spans="1:15">
+      <c r="O56" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="P56" s="2"/>
+    </row>
+    <row r="57" spans="1:16">
       <c r="A57" s="2">
         <v>8002</v>
       </c>
@@ -4116,16 +4318,16 @@
         <v>8002</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G57" s="11">
         <v>1</v>
@@ -4140,14 +4342,17 @@
         <v>1</v>
       </c>
       <c r="M57" s="12" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="N57" s="12">
         <v>500</v>
       </c>
-      <c r="O57" s="2"/>
-    </row>
-    <row r="58" spans="1:15">
+      <c r="O57" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="P57" s="2"/>
+    </row>
+    <row r="58" spans="1:16">
       <c r="A58" s="2">
         <v>8003</v>
       </c>
@@ -4155,16 +4360,16 @@
         <v>8003</v>
       </c>
       <c r="C58" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="F58" s="11" t="s">
         <v>189</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="F58" s="11" t="s">
-        <v>184</v>
       </c>
       <c r="G58" s="11">
         <v>1</v>
@@ -4179,12 +4384,15 @@
         <v>1</v>
       </c>
       <c r="M58" s="12" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="N58" s="12">
         <v>500</v>
       </c>
-      <c r="O58" s="2"/>
+      <c r="O58" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="P58" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Src/Data/Tables/ItemDefine.xlsx
+++ b/Src/Data/Tables/ItemDefine.xlsx
@@ -113,7 +113,7 @@
     <t>LimitClass</t>
   </si>
   <si>
-    <t>CanUes</t>
+    <t>CanUse</t>
   </si>
   <si>
     <t>UseCD</t>
@@ -1729,7 +1729,7 @@
     <tableColumn id="6" name="Category" dataDxfId="5"/>
     <tableColumn id="98" name="Level" dataDxfId="6"/>
     <tableColumn id="7" name="LimitClass" dataDxfId="7"/>
-    <tableColumn id="8" name="CanUes" dataDxfId="8"/>
+    <tableColumn id="8" name="CanUse" dataDxfId="8"/>
     <tableColumn id="9" name="UseCD" dataDxfId="9"/>
     <tableColumn id="10" name="Prise" dataDxfId="10"/>
     <tableColumn id="11" name="StackLimit" dataDxfId="11"/>
